--- a/filer/76220115_sg.xlsx
+++ b/filer/76220115_sg.xlsx
@@ -7596,7 +7596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7703,21 +7703,23 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
+          <t>fsa:PensionLiabilitiesRelatedToManagementCategory</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
-        </is>
-      </c>
-      <c r="D4" s="38" t="n"/>
-      <c r="E4" s="38" t="n"/>
+          <t>fsa:PensionLiabilitiesRelatedToManagementCategory</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="n">
+        <v>235</v>
+      </c>
+      <c r="E4" s="38" t="n">
+        <v>451</v>
+      </c>
       <c r="F4" s="38" t="n"/>
       <c r="G4" s="38" t="n"/>
-      <c r="H4" s="38" t="n">
-        <v>123</v>
-      </c>
+      <c r="H4" s="38" t="n"/>
       <c r="I4" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7732,53 +7734,22 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:PensionLiabilitiesRelatedToManagementCategory</t>
+          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:PensionLiabilitiesRelatedToManagementCategory</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>235</v>
-      </c>
-      <c r="E5" s="35" t="n">
-        <v>451</v>
-      </c>
+          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n"/>
       <c r="G5" s="35" t="n"/>
-      <c r="H5" s="35" t="n"/>
+      <c r="H5" s="35" t="n">
+        <v>-5331</v>
+      </c>
       <c r="I5" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
-        </is>
-      </c>
-      <c r="C6" s="37" t="inlineStr">
-        <is>
-          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="38" t="n"/>
-      <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n"/>
-      <c r="H6" s="38" t="n">
-        <v>-5331</v>
-      </c>
-      <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/76220115_sg.xlsx
+++ b/filer/76220115_sg.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision · Regnskabsår 1/5–30/4 (forskudt)</t>
         </is>
       </c>
     </row>

--- a/filer/76220115_sg.xlsx
+++ b/filer/76220115_sg.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4819,6 +4819,13 @@
       <c r="F99" s="13">
         <f>IFERROR($F$36/($F$61+$F$68)*100,"")</f>
         <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse ikke offentliggjort (jf. koncernfritagelse, ÅRL §86, stk. 4)</t>
+        </is>
       </c>
     </row>
   </sheetData>
